--- a/data/processed/daily_rosters_excels/roster_2025-12-25.xlsx
+++ b/data/processed/daily_rosters_excels/roster_2025-12-25.xlsx
@@ -979,16 +979,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4433083</v>
+        <v>3907497</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cam Spencer</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1642285</t>
+          <t>1627749</t>
         </is>
       </c>
     </row>
@@ -4171,26 +4171,26 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4576087</v>
+        <v>4278580</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Peyton Watson</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1631212</t>
+          <t>1630572</t>
         </is>
       </c>
     </row>
@@ -4703,26 +4703,26 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2990992</v>
+        <v>4278585</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>203935</t>
+          <t>1631221</t>
         </is>
       </c>
     </row>
@@ -5121,26 +5121,26 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3157465</v>
+        <v>4397002</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1629130</t>
+          <t>1630245</t>
         </is>
       </c>
     </row>
@@ -5159,26 +5159,26 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4397002</v>
+        <v>4278053</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1630245</t>
+          <t>1630558</t>
         </is>
       </c>
     </row>
@@ -5197,26 +5197,26 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4278053</v>
+        <v>6440</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PF</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1630558</t>
+          <t>202699</t>
         </is>
       </c>
     </row>
